--- a/data/glossary samp01.xlsx
+++ b/data/glossary samp01.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:U6"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -455,6 +455,18 @@
       <c r="Q1" s="1" t="str">
         <v>画像キャプション（第3言語）</v>
       </c>
+      <c r="R1" s="1" t="str">
+        <v>用語（第4言語）</v>
+      </c>
+      <c r="S1" s="1" t="str">
+        <v>概要（第4言語）</v>
+      </c>
+      <c r="T1" s="1" t="str">
+        <v>詳細（第4言語）</v>
+      </c>
+      <c r="U1" s="1" t="str">
+        <v>画像キャプション（第4言語）</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
@@ -508,6 +520,18 @@
       <c r="Q2" s="1" t="str">
         <v/>
       </c>
+      <c r="R2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="T2" s="1" t="str">
+        <v/>
+      </c>
+      <c r="U2" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
@@ -561,6 +585,18 @@
       <c r="Q3" s="1" t="str">
         <v/>
       </c>
+      <c r="R3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="T3" s="1" t="str">
+        <v/>
+      </c>
+      <c r="U3" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
@@ -614,6 +650,18 @@
       <c r="Q4" s="1" t="str">
         <v/>
       </c>
+      <c r="R4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="T4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="U4" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="str">
@@ -667,6 +715,18 @@
       <c r="Q5" s="1" t="str">
         <v/>
       </c>
+      <c r="R5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="T5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="U5" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="str">
@@ -720,17 +780,29 @@
       <c r="Q6" s="1" t="str">
         <v/>
       </c>
+      <c r="R6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="S6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="T6" s="1" t="str">
+        <v/>
+      </c>
+      <c r="U6" s="1" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="str">
@@ -751,6 +823,9 @@
       <c r="F1" s="1" t="str">
         <v>分類名（第3言語）</v>
       </c>
+      <c r="G1" s="1" t="str">
+        <v>分類名（第4言語）</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="str">
@@ -771,6 +846,9 @@
       <c r="F2" s="1" t="str">
         <v/>
       </c>
+      <c r="G2" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="str">
@@ -791,6 +869,9 @@
       <c r="F3" s="1" t="str">
         <v/>
       </c>
+      <c r="G3" s="1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="str">
@@ -811,10 +892,13 @@
       <c r="F4" s="1" t="str">
         <v/>
       </c>
+      <c r="G4" s="1" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
